--- a/TABLERO_PA_C.xlsx
+++ b/TABLERO_PA_C.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\OneDrive\Escritorio\Tableros de Control\2. Contraloría\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2a95cfba4fb0187/Escritorio/Tableros de Control/2. Contraloría/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{5037B3AD-B0A2-4521-8F49-D3B2F1605E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E578FF17-DE02-447B-99E5-1C7E6708F17A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="10" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="11" xr2:uid="{E38B2051-8614-49B4-943E-B3707D980583}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablero" sheetId="3" r:id="rId1"/>
@@ -24,12 +24,13 @@
     <sheet name="Cálculos" sheetId="4" r:id="rId9"/>
     <sheet name="Hoja1" sheetId="7" state="hidden" r:id="rId10"/>
     <sheet name="Base de Datos" sheetId="1" r:id="rId11"/>
-    <sheet name="Hoja3" sheetId="9" state="hidden" r:id="rId12"/>
-    <sheet name="Compromisos 1 trimestre" sheetId="8" r:id="rId13"/>
-    <sheet name="Hoja2" sheetId="6" state="hidden" r:id="rId14"/>
+    <sheet name="Enlace PDF" sheetId="17" r:id="rId12"/>
+    <sheet name="Hoja3" sheetId="9" state="hidden" r:id="rId13"/>
+    <sheet name="Compromisos 1 trimestre" sheetId="8" r:id="rId14"/>
+    <sheet name="Hoja2" sheetId="6" state="hidden" r:id="rId15"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId16"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Base de Datos'!$A$1:$AF$85</definedName>
@@ -40,15 +41,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId16"/>
-    <pivotCache cacheId="1" r:id="rId17"/>
+    <pivotCache cacheId="0" r:id="rId17"/>
+    <pivotCache cacheId="1" r:id="rId18"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId18"/>
         <x14:slicerCache r:id="rId19"/>
         <x14:slicerCache r:id="rId20"/>
+        <x14:slicerCache r:id="rId21"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -95,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2626" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2638" uniqueCount="812">
   <si>
     <t>No.</t>
   </si>
@@ -2681,6 +2682,46 @@
   </si>
   <si>
     <t>Se actualiza el Procedimiento Gestión y Recuperación de los Registros Susceptibles Código GPE-PR02 Versión 2 el cual se encuentra disponible en el SIG</t>
+  </si>
+  <si>
+    <t>Vigencia Auditoría</t>
+  </si>
+  <si>
+    <t>Nombre del Informe</t>
+  </si>
+  <si>
+    <t>Enlace PDF</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/u/0/folders/1Xr9YyjgouK7KDXNsneC4b6STF200hEJ8</t>
+  </si>
+  <si>
+    <t>Auditoría Financiera y de Gestión
+Terminal de Transporte S.A. -
+TTSA</t>
+  </si>
+  <si>
+    <t>PAD 88 - 2023</t>
+  </si>
+  <si>
+    <t>PAD 90 - 2024</t>
+  </si>
+  <si>
+    <t>Auditoría Financiera y de Gestión
+Terminal de Transporte S.A. - TTSA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/u/0/folders/1ysifagca3rJF1aTSms9Rl1eUuwU182KW</t>
+  </si>
+  <si>
+    <t>PAD 90 - 2025</t>
+  </si>
+  <si>
+    <t>Auditoría Financiera, de Gestión y Resultados
+Terminal de Transporte S.A. – TTSA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/u/0/folders/1f9Oe9ygA45IpwJ6a2AduFxL97Z70SE8i</t>
   </si>
 </sst>
 </file>
@@ -3188,7 +3229,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="217">
+  <cellXfs count="220">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3801,6 +3842,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5305,6 +5355,21 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="3" tint="0.499984740745262"/>
@@ -5411,21 +5476,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="left"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -20407,6 +20457,129 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+  </colItems>
+  <dataFields count="6">
+    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="5">
+    <format dxfId="240">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="239">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="238">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
+    </format>
+    <format dxfId="237">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="236">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5E7F1577-F431-4B0C-B786-3FF0F4829E0F}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A9:E35" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -20600,255 +20773,6 @@
     <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="255">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="254">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="253">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0"/>
-    </format>
-    <format dxfId="252">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="251">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="250">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="249">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="248">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="13"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="247">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="14"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="246">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="19"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="245">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="20"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="244">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="23"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="25"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="242">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="42"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="241">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="43"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="240">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="44"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="239">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="46"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="238">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="47"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="237">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="50"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="236">
-      <pivotArea dataOnly="0" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="12"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6C7AB91-8822-4E2E-BE9B-A9578BEEAA20}" name="TablaDinámica3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-    <i i="4">
-      <x v="4"/>
-    </i>
-    <i i="5">
-      <x v="5"/>
-    </i>
-  </colItems>
-  <dataFields count="6">
-    <dataField name="Cuenta de No. Hallazgo" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Total Planes de acción" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Abiertos" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Vencidos" fld="7" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Finalizados" fld="8" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Auditoría" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="5">
     <format dxfId="260">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -20862,13 +20786,139 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="256">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="255">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="254">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="253">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="13"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="252">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="14"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="251">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="19"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="250">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="20"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="249">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="23"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="248">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="25"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="247">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="42"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="246">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="43"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="245">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="44"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="244">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="46"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="243">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="47"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="242">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="50"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="241">
+      <pivotArea dataOnly="0" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="12"/>
           </reference>
         </references>
       </pivotArea>
@@ -29895,7 +29945,7 @@
       </c>
       <c r="AC9" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD9" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -29998,7 +30048,7 @@
       </c>
       <c r="AC10" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD10" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -30101,7 +30151,7 @@
       </c>
       <c r="AC11" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD11" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -30204,7 +30254,7 @@
       </c>
       <c r="AC12" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD12" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -30632,7 +30682,7 @@
       </c>
       <c r="AC16" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD16" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -31686,7 +31736,7 @@
       </c>
       <c r="AC26" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD26" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -31789,7 +31839,7 @@
       </c>
       <c r="AC27" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD27" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -31892,7 +31942,7 @@
       </c>
       <c r="AC28" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD28" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -31995,7 +32045,7 @@
       </c>
       <c r="AC29" s="68">
         <f t="shared" ca="1" si="0"/>
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="AD29" s="69">
         <f t="shared" ca="1" si="1"/>
@@ -38069,6 +38119,575 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56874FC2-BD66-4B35-8F27-CB6DD00D4B21}">
+  <dimension ref="A1:C105"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="23.21875" style="168" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="168" customWidth="1"/>
+    <col min="3" max="3" width="68.6640625" style="168" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>800</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>801</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="43.2">
+      <c r="A2" s="217" t="s">
+        <v>805</v>
+      </c>
+      <c r="B2" s="170" t="s">
+        <v>804</v>
+      </c>
+      <c r="C2" s="218" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="43.2">
+      <c r="A3" s="217" t="s">
+        <v>806</v>
+      </c>
+      <c r="B3" s="170" t="s">
+        <v>807</v>
+      </c>
+      <c r="C3" s="218" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="43.2">
+      <c r="A4" s="217" t="s">
+        <v>809</v>
+      </c>
+      <c r="B4" s="170" t="s">
+        <v>810</v>
+      </c>
+      <c r="C4" s="219" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="217"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="217"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="217"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="217"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="217"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="217"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="217"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="217"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="217"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="217"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="217"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="217"/>
+      <c r="B15" s="217"/>
+      <c r="C15" s="217"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="217"/>
+      <c r="B16" s="217"/>
+      <c r="C16" s="217"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="217"/>
+      <c r="B17" s="217"/>
+      <c r="C17" s="217"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="217"/>
+      <c r="B18" s="217"/>
+      <c r="C18" s="217"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="217"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="217"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="217"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="217"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="217"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="217"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="217"/>
+      <c r="B22" s="217"/>
+      <c r="C22" s="217"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="217"/>
+      <c r="B23" s="217"/>
+      <c r="C23" s="217"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="217"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="217"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="217"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="217"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="217"/>
+      <c r="B26" s="217"/>
+      <c r="C26" s="217"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="217"/>
+      <c r="B27" s="217"/>
+      <c r="C27" s="217"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="217"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="217"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="217"/>
+      <c r="B29" s="217"/>
+      <c r="C29" s="217"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="217"/>
+      <c r="B30" s="217"/>
+      <c r="C30" s="217"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="217"/>
+      <c r="B31" s="217"/>
+      <c r="C31" s="217"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="217"/>
+      <c r="B32" s="217"/>
+      <c r="C32" s="217"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="217"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="217"/>
+      <c r="B34" s="217"/>
+      <c r="C34" s="217"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="217"/>
+      <c r="B35" s="217"/>
+      <c r="C35" s="217"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="217"/>
+      <c r="B36" s="217"/>
+      <c r="C36" s="217"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="217"/>
+      <c r="B37" s="217"/>
+      <c r="C37" s="217"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="217"/>
+      <c r="B38" s="217"/>
+      <c r="C38" s="217"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="217"/>
+      <c r="B39" s="217"/>
+      <c r="C39" s="217"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="217"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="217"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="217"/>
+      <c r="B41" s="217"/>
+      <c r="C41" s="217"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="217"/>
+      <c r="B42" s="217"/>
+      <c r="C42" s="217"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="217"/>
+      <c r="B43" s="217"/>
+      <c r="C43" s="217"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="217"/>
+      <c r="B44" s="217"/>
+      <c r="C44" s="217"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="217"/>
+      <c r="B45" s="217"/>
+      <c r="C45" s="217"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="217"/>
+      <c r="B46" s="217"/>
+      <c r="C46" s="217"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="217"/>
+      <c r="B47" s="217"/>
+      <c r="C47" s="217"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="217"/>
+      <c r="B48" s="217"/>
+      <c r="C48" s="217"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="217"/>
+      <c r="B49" s="217"/>
+      <c r="C49" s="217"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="217"/>
+      <c r="B50" s="217"/>
+      <c r="C50" s="217"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="217"/>
+      <c r="B51" s="217"/>
+      <c r="C51" s="217"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="217"/>
+      <c r="B52" s="217"/>
+      <c r="C52" s="217"/>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="217"/>
+      <c r="B53" s="217"/>
+      <c r="C53" s="217"/>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="217"/>
+      <c r="B54" s="217"/>
+      <c r="C54" s="217"/>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="217"/>
+      <c r="B55" s="217"/>
+      <c r="C55" s="217"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="217"/>
+      <c r="B56" s="217"/>
+      <c r="C56" s="217"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="217"/>
+      <c r="B57" s="217"/>
+      <c r="C57" s="217"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="217"/>
+      <c r="B58" s="217"/>
+      <c r="C58" s="217"/>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="217"/>
+      <c r="B59" s="217"/>
+      <c r="C59" s="217"/>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="217"/>
+      <c r="B60" s="217"/>
+      <c r="C60" s="217"/>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="217"/>
+      <c r="B61" s="217"/>
+      <c r="C61" s="217"/>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="217"/>
+      <c r="B62" s="217"/>
+      <c r="C62" s="217"/>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="217"/>
+      <c r="B63" s="217"/>
+      <c r="C63" s="217"/>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="217"/>
+      <c r="B64" s="217"/>
+      <c r="C64" s="217"/>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="217"/>
+      <c r="B65" s="217"/>
+      <c r="C65" s="217"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="217"/>
+      <c r="B66" s="217"/>
+      <c r="C66" s="217"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="217"/>
+      <c r="B67" s="217"/>
+      <c r="C67" s="217"/>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="217"/>
+      <c r="B68" s="217"/>
+      <c r="C68" s="217"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="217"/>
+      <c r="B69" s="217"/>
+      <c r="C69" s="217"/>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="217"/>
+      <c r="B70" s="217"/>
+      <c r="C70" s="217"/>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="217"/>
+      <c r="B71" s="217"/>
+      <c r="C71" s="217"/>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="217"/>
+      <c r="B72" s="217"/>
+      <c r="C72" s="217"/>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="217"/>
+      <c r="B73" s="217"/>
+      <c r="C73" s="217"/>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="217"/>
+      <c r="B74" s="217"/>
+      <c r="C74" s="217"/>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="217"/>
+      <c r="B75" s="217"/>
+      <c r="C75" s="217"/>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="217"/>
+      <c r="B76" s="217"/>
+      <c r="C76" s="217"/>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="217"/>
+      <c r="B77" s="217"/>
+      <c r="C77" s="217"/>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="217"/>
+      <c r="B78" s="217"/>
+      <c r="C78" s="217"/>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="217"/>
+      <c r="B79" s="217"/>
+      <c r="C79" s="217"/>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="217"/>
+      <c r="B80" s="217"/>
+      <c r="C80" s="217"/>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="217"/>
+      <c r="B81" s="217"/>
+      <c r="C81" s="217"/>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="217"/>
+      <c r="B82" s="217"/>
+      <c r="C82" s="217"/>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="217"/>
+      <c r="B83" s="217"/>
+      <c r="C83" s="217"/>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="217"/>
+      <c r="B84" s="217"/>
+      <c r="C84" s="217"/>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="217"/>
+      <c r="B85" s="217"/>
+      <c r="C85" s="217"/>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="217"/>
+      <c r="B86" s="217"/>
+      <c r="C86" s="217"/>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="217"/>
+      <c r="B87" s="217"/>
+      <c r="C87" s="217"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="217"/>
+      <c r="B88" s="217"/>
+      <c r="C88" s="217"/>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="217"/>
+      <c r="B89" s="217"/>
+      <c r="C89" s="217"/>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="217"/>
+      <c r="B90" s="217"/>
+      <c r="C90" s="217"/>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="217"/>
+      <c r="B91" s="217"/>
+      <c r="C91" s="217"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="217"/>
+      <c r="B92" s="217"/>
+      <c r="C92" s="217"/>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="217"/>
+      <c r="B93" s="217"/>
+      <c r="C93" s="217"/>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="217"/>
+      <c r="B94" s="217"/>
+      <c r="C94" s="217"/>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="217"/>
+      <c r="B95" s="217"/>
+      <c r="C95" s="217"/>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="217"/>
+      <c r="B96" s="217"/>
+      <c r="C96" s="217"/>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="217"/>
+      <c r="B97" s="217"/>
+      <c r="C97" s="217"/>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="217"/>
+      <c r="B98" s="217"/>
+      <c r="C98" s="217"/>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="217"/>
+      <c r="B99" s="217"/>
+      <c r="C99" s="217"/>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="217"/>
+      <c r="B100" s="217"/>
+      <c r="C100" s="217"/>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="217"/>
+      <c r="B101" s="217"/>
+      <c r="C101" s="217"/>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="217"/>
+      <c r="B102" s="217"/>
+      <c r="C102" s="217"/>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="217"/>
+      <c r="B103" s="217"/>
+      <c r="C103" s="217"/>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="217"/>
+      <c r="B104" s="217"/>
+      <c r="C104" s="217"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="217"/>
+      <c r="B105" s="217"/>
+      <c r="C105" s="217"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{89386E12-4C8F-4898-8882-A7E5AE74C24C}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{F498949F-1D31-4693-8C36-7C60DD4FCF71}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{B6B2E46D-F350-4F55-88FE-79FD624E7D57}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70FCFBCC-97BE-43AA-8755-E8029D42D9C7}">
   <sheetPr codeName="Hoja9"/>
   <dimension ref="C2:J10"/>
@@ -38131,7 +38750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CD58B18-6732-4661-826E-4F36939F10AB}">
   <sheetPr codeName="Hoja10">
     <tabColor rgb="FFFFC000"/>
@@ -39124,7 +39743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BFFF0AA-7584-4052-9219-58E9E2460C78}">
   <sheetPr codeName="Hoja6"/>
   <dimension ref="A1:AF4"/>
